--- a/artfynd/A 31523-2022 artfynd.xlsx
+++ b/artfynd/A 31523-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,63 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114927327</v>
+        <v>114926163</v>
       </c>
       <c r="B2" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80305</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Råberget (Råberget), Upl</t>
+          <t>Naturskog N Råberget, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696007</v>
+        <v>696064</v>
       </c>
       <c r="R2" t="n">
-        <v>6606789</v>
+        <v>6606792</v>
       </c>
       <c r="S2" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-02-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2024-02-28</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Endast noterad på en asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,31 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
+          <t>Ola Hammarström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Martin Permats</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+          <t>Ola Hammarström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114928531</v>
+        <v>114927327</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,38 +788,47 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Råberget (Råberget), Upl</t>
+          <t>Råberget, Råberget, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>695888</v>
+        <v>696007</v>
       </c>
       <c r="R3" t="n">
-        <v>6606763</v>
+        <v>6606789</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,12 +901,7 @@
         <v>114928568</v>
       </c>
       <c r="B4" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -964,7 +939,7 @@
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Råberget (Råberget), Upl</t>
+          <t>Råberget, Råberget, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1039,6 +1014,235 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114928531</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Råberget, Råberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>695888</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6606763</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-02-29</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Martin Permats</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108662758</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Råberget, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>695846</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6607033</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-05-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Tjäderinventering i Tärnanområdet</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 31523-2022 artfynd.xlsx
+++ b/artfynd/A 31523-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114926163</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114927327</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114928568</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1128,6 +1148,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114928531</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1245,8 +1270,20 @@
           <t>Tjäderinventering i Tärnanområdet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108662758</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>